--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Bernard Yannou, Gregoire Burge</t>
+          <t>Bernard Yannou, Gregoire Burgé</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Bernard Yannou, Gregoire Burge</t>
+          <t>Bernard Yannou, Gregoire Burgé</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
+          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
+          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
+          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Fatoumata Aonon, Stephanie Oger-Roussel</t>
+          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Fatoumata Aonon, Stephanie Oger-Roussel</t>
+          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Pascal Corbel</t>
+          <t>Arielle Santé, Pascal Corbel</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Pascal Corbel</t>
+          <t>Arielle Santé, Pascal Corbel</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Joel Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Joël Nguen, Pascal Corbel</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Joel Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Joël Nguen, Pascal Corbel</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Bernard Yannou, Joel Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Bernard Yannou, Joël Nguen, Pascal Corbel</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Arielle Sante, Bernard Yannou, Joel Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Bernard Yannou, Joël Nguen, Pascal Corbel</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-sante.doc</t>
+          <t>guide_editorial_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Eneli Vino, Fatoumata Aonon, Remi Wache, Soizic Lefeuvre, Virginia Branco</t>
+          <t>Eneli Vino, Fatoumata Aonon, Rémi Waché, Soizic Lefeuvre, Virginia Branco</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Eneli Vino, Fatoumata Aonon, Remi Wache, Soizic Lefeuvre, Virginia Branco</t>
+          <t>Eneli Vino, Fatoumata Aonon, Rémi Waché, Soizic Lefeuvre, Virginia Branco</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Joël Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Pascal Corbel</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Joël Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Pascal Corbel</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Bernard Yannou, Joël Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Bernard Yannou, Pascal Corbel</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Bernard Yannou, Joël Nguen, Pascal Corbel</t>
+          <t>Arielle Santé, Bernard Yannou, Pascal Corbel</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -528,10 +528,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>E1.txt</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>video_expert_E1.html</t>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_bernard-yannou.doc</t>
+          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_bernard-yannou.doc</t>
+          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_bernard-yannou.doc</t>
+          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
@@ -772,10 +772,14 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>E6.txt</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>video_expert_E6.html</t>
@@ -783,7 +787,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
         </is>
       </c>
     </row>
@@ -831,7 +835,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
         </is>
       </c>
     </row>
@@ -879,7 +883,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
         </is>
       </c>
     </row>
@@ -927,7 +931,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
         </is>
       </c>
     </row>
@@ -975,7 +979,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1027,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1075,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1123,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1171,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1219,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1267,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1315,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1411,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1459,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1471,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Gérer les freins. Temps, légitimité, entourage, droit à l’apprentissage et sécurisation du parcours.</t>
+          <t>Concilier recherche et engagement dans l'innovation. Double casquette, gouvernance, impartialité, évolution du métier de chercheur.</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1503,7 +1507,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1519,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Innover comme processus d’apprentissage. Incertitude, essais, erreurs, pivot et progression plutôt que réussite linéaire. (focaliser le discours sur les leviers existant pour vaincre les freins)</t>
+          <t>Gérer les freins et innover comme apprentissage. Temps, légitimité, entourage, doute ; incertitude, essais, pivot ; première action réversible.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1551,7 +1555,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1603,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_eneli-vino.doc</t>
+          <t>guide_editorial_simplifie_eneli-vino.doc</t>
         </is>
       </c>
     </row>
@@ -1636,10 +1640,14 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>E23.txt</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
           <t>video_expert_E23.html</t>
@@ -1647,7 +1655,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_eneli-vino.doc</t>
+          <t>guide_editorial_simplifie_eneli-vino.doc</t>
         </is>
       </c>
     </row>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bernard Yannou, Eneli Vino</t>
+          <t>Retenu : Bernard Yannou</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Bernard Yannou, Gregoire Burgé</t>
+          <t>Retenu : Gregoire Burgé</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
+          <t>guide_editorial_simplifie_gregoire-burgé.doc</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Bernard Yannou, Gregoire Burgé</t>
+          <t>Retenu : Gregoire Burgé</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
+          <t>guide_editorial_simplifie_gregoire-burgé.doc</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon, Stephanie Oger-Roussel, Virginia Branco</t>
+          <t>Retenu : Stephanie Oger-Roussel</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_stephanie-oger-roussel.doc</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon, Stephanie Oger-Roussel, Virginia Branco</t>
+          <t>Retenu : Virginia Branco</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_virginia-branco.doc</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Antoine Latreille, Eneli Vino, Soizic Lefeuvre, Stephanie Sano</t>
+          <t>Retenu : Stephanie Sano</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_stephanie-sano.doc</t>
         </is>
       </c>
     </row>
@@ -819,15 +819,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Antoine Latreille, Eneli Vino, Soizic Lefeuvre, Stephanie Sano</t>
+          <t>Retenu : Arielle Santé, Stephanie Sano</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>E7.txt</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>video_expert_E7.html</t>
@@ -835,7 +839,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -867,7 +871,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Antoine Latreille, Eneli Vino, Soizic Lefeuvre, Stanislas De Lapasse</t>
+          <t>Retenu : Arielle Santé, Stanislas De Lapasse</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -915,7 +919,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Antoine Latreille, Eneli Vino, Soizic Lefeuvre, Stanislas De Lapasse</t>
+          <t>Retenu : Antoine Latreille, Stanislas De Lapasse</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -963,7 +967,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon, Soizic Lefeuvre, Stephanie Oger-Roussel, Virginia Branco</t>
+          <t>Retenu : Arielle Santé, Virginia Branco</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1015,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon, Soizic Lefeuvre, Stephanie Oger-Roussel, Virginia Branco</t>
+          <t>Retenu : Soizic Lefeuvre</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1027,7 +1031,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_soizic-lefeuvre.doc</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1063,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
+          <t>Retenu : Fatoumata Aonon</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1075,7 +1079,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1159,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
+          <t>Retenu : Yoann Montenot</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_yoann-montenot.doc</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel</t>
+          <t>Retenu : Fatoumata Aonon</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1219,7 +1223,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1303,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Pascal Corbel</t>
+          <t>Retenu : Pascal Corbel</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1315,7 +1319,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1447,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Pascal Corbel</t>
+          <t>Retenu : Pascal Corbel</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1459,7 +1463,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1495,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Bernard Yannou, Pascal Corbel</t>
+          <t>Retenu : Bernard Yannou</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1507,7 +1511,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1543,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Bernard Yannou, Pascal Corbel</t>
+          <t>Retenu : Pascal Corbel</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1555,7 +1559,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1571,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Pascal Corbel : Concevoir une collaboration équilibrée. Objectifs partagés, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+          <t>Concevoir une collaboration équilibrée. Objectifs partagés, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1587,7 +1591,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Eneli Vino, Fatoumata Aonon, Rémi Waché, Soizic Lefeuvre, Virginia Branco</t>
+          <t>Retenu : Rémi Waché</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1603,7 +1607,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_eneli-vino.doc</t>
+          <t>guide_editorial_simplifie_rémi-waché.doc</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1619,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Antoine Latreille : Sécuriser juridiquement la collaboration. Confidentialité, contrats, connaissances antérieures, résultats nouveaux, PI, publication et sortie du partenariat.</t>
+          <t>Sécuriser juridiquement la collaboration. Confidentialité, contrats, connaissances antérieures, résultats nouveaux, PI, publication et sortie du partenariat.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1635,7 +1639,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Eneli Vino, Fatoumata Aonon, Rémi Waché, Soizic Lefeuvre, Virginia Branco</t>
+          <t>Retenu : Eneli Vino</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -876,10 +876,14 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>E8.txt</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>video_expert_E8.html</t>
@@ -924,10 +928,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>E9.txt</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>video_expert_E9.html</t>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -724,10 +724,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>E5.txt</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>video_expert_E5.html</t>
@@ -980,10 +984,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>E10.txt</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>video_expert_E10.html</t>
@@ -1508,10 +1516,14 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>E20.txt</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>video_expert_E20.html</t>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Arielle Santé, Stephanie Sano</t>
+          <t>Retenu : Stephanie Sano</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_stephanie-sano.doc</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Arielle Santé, Stanislas De Lapasse</t>
+          <t>Retenu : Stanislas De Lapasse</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_stanislas-de-lapasse.doc</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Antoine Latreille, Stanislas De Lapasse</t>
+          <t>Retenu : Stanislas De Lapasse</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_stanislas-de-lapasse.doc</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Arielle Santé, Virginia Branco</t>
+          <t>Retenu : Virginia Branco</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_virginia-branco.doc</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel, Yoann Montenot</t>
+          <t>Retenu : Arielle Santé</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Fatoumata Aonon, Stephanie Oger-Roussel</t>
+          <t>Retenu : Arielle Santé</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Pascal Corbel</t>
+          <t>Retenu : Antoine Latreille</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé, Pascal Corbel</t>
+          <t>Retenu : Arielle Santé</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -1324,10 +1324,14 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>E16.txt</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>video_expert_E16.html</t>
@@ -1468,10 +1472,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>E19.txt</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>video_expert_E19.html</t>
@@ -1543,7 +1551,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Gérer les freins et innover comme apprentissage. Temps, légitimité, entourage, doute ; incertitude, essais, pivot ; première action réversible.</t>
+          <t>Innover comme processus d’apprentissage. Incertitude, essais, erreurs, pivot et progression plutôt que réussite linéaire ; leviers existants pour dépasser les freins.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1568,10 +1576,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>E21.txt</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>video_expert_E21.html</t>
